--- a/Extracted_data_analysis/global/Output-Transformed_data/summary_counts_question_4.xlsx
+++ b/Extracted_data_analysis/global/Output-Transformed_data/summary_counts_question_4.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
   <si>
     <t xml:space="preserve">meso_design</t>
   </si>
@@ -324,6 +324,9 @@
     <t xml:space="preserve">site(sample)+site(transect)</t>
   </si>
   <si>
+    <t xml:space="preserve">site(specimen)</t>
+  </si>
+  <si>
     <t xml:space="preserve">site(stationary)</t>
   </si>
   <si>
@@ -753,6 +756,9 @@
     <t xml:space="preserve">ph+salinity+temperature</t>
   </si>
   <si>
+    <t xml:space="preserve">poc+pom</t>
+  </si>
+  <si>
     <t xml:space="preserve">pollutant</t>
   </si>
   <si>
@@ -769,6 +775,9 @@
   </si>
   <si>
     <t xml:space="preserve">rugosity+slope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rugosity+slope+turbidity</t>
   </si>
   <si>
     <t xml:space="preserve">salinity</t>
@@ -1199,10 +1208,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4">
@@ -1320,10 +1329,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -1477,7 +1486,7 @@
         <v>81</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="29">
@@ -1727,10 +1736,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C51" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="52">
@@ -1848,7 +1857,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C62" t="n">
         <v>9.2</v>
@@ -1983,7 +1992,7 @@
         <v>83</v>
       </c>
       <c r="C74" t="n">
-        <v>9.2</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="75">
@@ -2156,10 +2165,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C90" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="91">
@@ -2244,10 +2253,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C98" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="99">
@@ -2277,10 +2286,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="102">
@@ -2288,10 +2297,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="103">
@@ -2310,10 +2319,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>3.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="105">
@@ -2321,10 +2330,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C105" t="n">
-        <v>0.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="106">
@@ -2332,10 +2341,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="107">
@@ -2343,10 +2352,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="108">
@@ -2354,10 +2363,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="109">
@@ -2365,10 +2374,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="110">
@@ -2376,10 +2385,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="C110" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="111">
@@ -2387,10 +2396,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="112">
@@ -2431,10 +2440,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="116">
@@ -2442,10 +2451,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="117">
@@ -2464,10 +2473,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>4.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="119">
@@ -2475,10 +2484,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C119" t="n">
-        <v>0.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="120">
@@ -2497,10 +2506,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="122">
@@ -2508,10 +2517,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="123">
@@ -2519,10 +2528,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="124">
@@ -2530,10 +2539,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="C124" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="125">
@@ -2541,10 +2550,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="126">
@@ -2574,10 +2583,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="129">
@@ -2585,10 +2594,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C129" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -2596,10 +2605,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="131">
@@ -2607,10 +2616,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="132">
@@ -2618,10 +2627,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="133">
@@ -2640,10 +2649,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C134" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="135">
@@ -2651,10 +2660,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="136">
@@ -2684,10 +2693,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="139">
@@ -2695,10 +2704,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -2706,9 +2715,20 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C140" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>142</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2725,7 +2745,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2747,24 +2767,24 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" t="n">
         <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" t="n">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C4" t="n">
-        <v>92.1</v>
+        <v>92.2</v>
       </c>
     </row>
   </sheetData>
@@ -2780,7 +2800,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2802,21 +2822,21 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" t="n">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C3" t="n">
-        <v>72.9</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C4" t="n">
         <v>26.4</v>
@@ -2835,7 +2855,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2846,18 +2866,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" t="n">
         <v>36</v>
@@ -2868,13 +2888,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C4" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="5">
@@ -2890,13 +2910,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B6" t="n">
         <v>540</v>
       </c>
       <c r="C6" t="n">
-        <v>58.3</v>
+        <v>57.9</v>
       </c>
     </row>
   </sheetData>
@@ -2912,7 +2932,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2923,7 +2943,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -2934,7 +2954,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -2945,7 +2965,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -2956,7 +2976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -2967,7 +2987,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -2978,7 +2998,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -2989,7 +3009,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -3000,7 +3020,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -3011,7 +3031,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -3022,7 +3042,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
@@ -3033,7 +3053,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -3044,7 +3064,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -3055,7 +3075,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="n">
         <v>2</v>
@@ -3066,7 +3086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -3077,7 +3097,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -3088,7 +3108,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -3099,7 +3119,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -3110,7 +3130,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
@@ -3121,7 +3141,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
@@ -3132,7 +3152,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
@@ -3143,7 +3163,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -3154,7 +3174,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
@@ -3165,7 +3185,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
@@ -3176,7 +3196,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
@@ -3187,7 +3207,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -3198,7 +3218,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -3209,7 +3229,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" t="n">
         <v>1</v>
@@ -3220,7 +3240,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
@@ -3231,7 +3251,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B30" t="n">
         <v>3</v>
@@ -3242,7 +3262,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B31" t="n">
         <v>3</v>
@@ -3253,7 +3273,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -3264,7 +3284,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B33" t="n">
         <v>1</v>
@@ -3275,7 +3295,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B34" t="n">
         <v>1</v>
@@ -3286,7 +3306,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -3297,7 +3317,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
@@ -3308,7 +3328,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B37" t="n">
         <v>1</v>
@@ -3319,7 +3339,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B38" t="n">
         <v>1</v>
@@ -3330,7 +3350,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B39" t="n">
         <v>1</v>
@@ -3341,7 +3361,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B40" t="n">
         <v>1</v>
@@ -3352,7 +3372,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B41" t="n">
         <v>1</v>
@@ -3363,7 +3383,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
@@ -3374,7 +3394,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
@@ -3385,7 +3405,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
@@ -3396,7 +3416,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
@@ -3407,18 +3427,18 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B47" t="n">
         <v>2</v>
@@ -3429,7 +3449,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B48" t="n">
         <v>1</v>
@@ -3440,7 +3460,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B49" t="n">
         <v>2</v>
@@ -3451,7 +3471,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B50" t="n">
         <v>1</v>
@@ -3462,7 +3482,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B51" t="n">
         <v>1</v>
@@ -3473,7 +3493,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B52" t="n">
         <v>2</v>
@@ -3484,7 +3504,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B53" t="n">
         <v>1</v>
@@ -3495,7 +3515,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B54" t="n">
         <v>1</v>
@@ -3506,7 +3526,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B55" t="n">
         <v>1</v>
@@ -3517,7 +3537,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" t="n">
         <v>1</v>
@@ -3528,7 +3548,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B57" t="n">
         <v>1</v>
@@ -3539,7 +3559,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" t="n">
         <v>1</v>
@@ -3550,7 +3570,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B59" t="n">
         <v>1</v>
@@ -3561,7 +3581,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" t="n">
         <v>1</v>
@@ -3572,7 +3592,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B61" t="n">
         <v>1</v>
@@ -3583,7 +3603,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B62" t="n">
         <v>21</v>
@@ -3594,7 +3614,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B63" t="n">
         <v>1</v>
@@ -3605,7 +3625,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B64" t="n">
         <v>1</v>
@@ -3616,7 +3636,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B65" t="n">
         <v>1</v>
@@ -3627,7 +3647,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" t="n">
         <v>3</v>
@@ -3638,7 +3658,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B67" t="n">
         <v>1</v>
@@ -3649,7 +3669,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B68" t="n">
         <v>1</v>
@@ -3660,7 +3680,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B69" t="n">
         <v>1</v>
@@ -3671,7 +3691,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B70" t="n">
         <v>2</v>
@@ -3682,7 +3702,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -3693,7 +3713,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B72" t="n">
         <v>7</v>
@@ -3704,7 +3724,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B73" t="n">
         <v>1</v>
@@ -3715,7 +3735,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B74" t="n">
         <v>2</v>
@@ -3726,7 +3746,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B75" t="n">
         <v>17</v>
@@ -3737,7 +3757,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B76" t="n">
         <v>1</v>
@@ -3770,18 +3790,18 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B79" t="n">
         <v>537</v>
       </c>
       <c r="C79" t="n">
-        <v>57.9</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B80" t="n">
         <v>1</v>
@@ -3792,7 +3812,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B81" t="n">
         <v>1</v>
@@ -3803,7 +3823,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B82" t="n">
         <v>1</v>
@@ -3814,7 +3834,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B83" t="n">
         <v>1</v>
@@ -3825,7 +3845,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B84" t="n">
         <v>2</v>
@@ -3836,7 +3856,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B85" t="n">
         <v>2</v>
@@ -3847,7 +3867,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B86" t="n">
         <v>1</v>
@@ -3858,7 +3878,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B87" t="n">
         <v>3</v>
@@ -3869,7 +3889,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B88" t="n">
         <v>1</v>
@@ -3880,7 +3900,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B89" t="n">
         <v>1</v>
@@ -3891,7 +3911,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B90" t="n">
         <v>1</v>
@@ -3902,7 +3922,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B91" t="n">
         <v>1</v>
@@ -3913,7 +3933,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B92" t="n">
         <v>1</v>
@@ -3924,7 +3944,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B93" t="n">
         <v>3</v>
@@ -3935,7 +3955,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B94" t="n">
         <v>1</v>
@@ -3946,7 +3966,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B95" t="n">
         <v>1</v>
@@ -3957,7 +3977,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B96" t="n">
         <v>2</v>
@@ -3968,7 +3988,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B97" t="n">
         <v>1</v>
@@ -3979,7 +3999,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B98" t="n">
         <v>1</v>
@@ -3990,7 +4010,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B99" t="n">
         <v>1</v>
@@ -4001,7 +4021,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B100" t="n">
         <v>1</v>
@@ -4012,7 +4032,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B101" t="n">
         <v>1</v>
@@ -4023,51 +4043,51 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C103" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -4078,18 +4098,18 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B108" t="n">
         <v>1</v>
@@ -4100,117 +4120,117 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B111" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C111" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B113" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C113" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B114" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B115" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C116" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B118" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>5.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B119" t="n">
         <v>1</v>
@@ -4221,84 +4241,84 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C120" t="n">
-        <v>0.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B122" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="C122" t="n">
-        <v>5.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B127" t="n">
         <v>1</v>
@@ -4309,23 +4329,45 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>277</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>278</v>
+      </c>
+      <c r="B131" t="n">
         <v>3</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C131" t="n">
         <v>0.3</v>
       </c>
     </row>
